--- a/output/2026-10-04_21_Malesia_Selangor_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-04_21_Malesia_Selangor_Componentistica_Ventilazione_industriale.xlsx
@@ -484,10 +484,9 @@
           <t>+603-7846 0340</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (redirect da eltafans.asia a elta.asia confermato) e dati forniti. Produttore di ventilatori industriali/commerciali con rete di distributori internazionali; scope aziendale include sales/fabrication/assembly/warehousing/distribution. Sede Shah Alam, Selangor. Email non verificata.</t>
+          <t>Verificato via sito ufficiale (redirect da eltafans.asia a elta.asia confermato) e dati forniti. Produttore di ventilatori industriali/commerciali con rete di distributori internazionali; scope aziendale include sales/fabrication/assembly/warehousing/distribution. Sede Shah Alam, Selangor. Email non verificata. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -517,11 +516,9 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web: e-shop B2B con categoria dedicata 'Fans &amp; Ventilation', descritto come distributore di utensili/ferramenta e prodotti di ventilazione operante da oltre 40 anni in area Petaling Jaya (Selangor). Indirizzo esatto, telefono ed email non reperiti da fonte affidabile: lasciati vuoti.</t>
+          <t>Verificato via ricerca web: e-shop B2B con categoria dedicata 'Fans &amp; Ventilation', descritto come distributore di utensili/ferramenta e prodotti di ventilazione operante da oltre 40 anni in area Petaling Jaya (Selangor). Indirizzo esatto, telefono ed email non reperiti da fonte affidabile: lasciati vuoti. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -536,7 +533,6 @@
           <t>Master Jaya Environmental Sdn Bhd (brand AIRBOSS)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -552,7 +548,6 @@
           <t>603-8962 6233</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato via ricerca web (Matrade, AHK Malaysia-German Chamber, Eco-Web): Engineering/Consultancy/Contracting/Manufacturing dal 1983, sede Wisma Master Jaya, Jalan Taming 3, Seri Kembangan, Selangor. Fornisce impianti di controllo inquinamento aria/ventilazione industriale (brand AIRBOSS) come fornitore B2B diretto a clienti industriali in vari paesi ASEAN; non è un utilizzatore finale del prodotto ma un produttore/fornitore del settore. Email non verificata.</t>
@@ -560,7 +555,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -570,7 +565,6 @@
           <t>MayAir Manufacturing (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -581,11 +575,9 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (Hiredly, MMU Career Connect, MedicalExpo): produttore/sviluppatore globale di soluzioni di purificazione aria dal 2001, sede 41 Jalan Anggerik Mokara 31/64, Kota Kemuning, Shah Alam, Selangor. Attivita' comprende R&amp;D, produzione, DISTRIBUZIONE, installazione e manutenzione di filtri HVAC/HEPA/FFU: fornitore B2B diretto, non cliente finale. Telefono ed email non reperiti da fonte affidabile.</t>
+          <t>Verificato via ricerca web (Hiredly, MMU Career Connect, MedicalExpo): produttore/sviluppatore globale di soluzioni di purificazione aria dal 2001, sede 41 Jalan Anggerik Mokara 31/64, Kota Kemuning, Shah Alam, Selangor. Attivita' comprende R&amp;D, produzione, DISTRIBUZIONE, installazione e manutenzione di filtri HVAC/HEPA/FFU: fornitore B2B diretto, non cliente finale. Telefono ed email non reperiti da fonte affidabile. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -600,7 +592,6 @@
           <t>DAV Engineering Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -611,11 +602,9 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (ExportHub): produttore e rivenditore (manufacturer and retailer) di dust collector, blower fan, trasportatori pneumatici/a vite, condotte, valvole rotative, dal 1970, sede Shah Alam, Selangor. Esporta in Thailandia, Corea, UK, Canada, Indonesia: fornitore B2B diretto. Sito web, telefono ed email non reperiti da fonte affidabile.</t>
+          <t>Verificato via ricerca web (ExportHub): produttore e rivenditore (manufacturer and retailer) di dust collector, blower fan, trasportatori pneumatici/a vite, condotte, valvole rotative, dal 1970, sede Shah Alam, Selangor. Esporta in Thailandia, Corea, UK, Canada, Indonesia: fornitore B2B diretto. Sito web, telefono ed email non reperiti da fonte affidabile. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -645,11 +634,9 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (Dun &amp; Bradstreet): sede Lot 1565 Jalan Kusta Perindustrian Kampung Jaya, Sungai Buloh, Selangor 47000. Filiale malese del gruppo Systemair (brand Systemair/Frico/Fantech/Menerga), leader globale ventilazione, vende tramite rete di distributori/installatori: fornitore B2B diretto. Sito locale dedicato non identificato (indicato dominio gruppo); telefono ed email non reperiti.</t>
+          <t>Verificato via ricerca web (Dun &amp; Bradstreet): sede Lot 1565 Jalan Kusta Perindustrian Kampung Jaya, Sungai Buloh, Selangor 47000. Filiale malese del gruppo Systemair (brand Systemair/Frico/Fantech/Menerga), leader globale ventilazione, vende tramite rete di distributori/installatori: fornitore B2B diretto. Sito locale dedicato non identificato (indicato dominio gruppo); telefono ed email non reperiti. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -664,7 +651,6 @@
           <t>Torin Industries (Malaysia) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -675,8 +661,6 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificato via ricerca web (Matrade, BSI client directory): produttore dal 2003 di ventilatori centrifughi/crossflow/elicoidali brand TORIN, certificazione ISO 9000 e BS 848, sede 6536A Jalan Bkt Kemuning, Section 34, Shah Alam, Selangor. Esporta in Australia, Nuova Zelanda, Indonesia tramite canali commerciali/OEM: fornitore B2B diretto, non produttore puro ad uso interno. Telefono/email non reperiti.</t>
@@ -684,7 +668,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -721,7 +705,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale: trading/distribution company con 40 anni di esperienza, rappresenta brand quali Siemens, Motovario, Delta, NTN; prodotti includono motori, inverter, pompe, ventilatori e blower. Sede No 8, Jalan TPP 6/7, Taman Perindustrian Puchong, Selangor. Distributore B2B confermato.</t>
+          <t>Verificato via sito ufficiale: trading/distribution company con 40 anni di esperienza, rappresenta brand quali Siemens, Motovario, Delta, NTN; prodotti includono motori, inverter, pompe, ventilatori e blower. Sede No 8, Jalan TPP 6/7, Taman Perindustrian Puchong, Selangor. Distributore B2B confermato. [DUPLICATO — vedi anche: 2026-10-04_20_Malesia_Selangor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -763,7 +747,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale: produttore/distributore globale di soluzioni di filtrazione aria (HEPA/EPA, bag filter, gas phase, containment), sede Lot 6 Jalan Pengapit 15/19, Seksyen 15, Shah Alam, Selangor. Opera con uffici regionali e rapporti diretti con clienti in piu' paesi: fornitore B2B diretto. Email aggiornata rispetto a quella fornita (vuota) nella lista grezza.</t>
+          <t>Verificato via sito ufficiale: produttore/distributore globale di soluzioni di filtrazione aria (HEPA/EPA, bag filter, gas phase, containment), sede Lot 6 Jalan Pengapit 15/19, Seksyen 15, Shah Alam, Selangor. Opera con uffici regionali e rapporti diretti con clienti in piu' paesi: fornitore B2B diretto. Email aggiornata rispetto a quella fornita (vuota) nella lista grezza. [DUPLICATO — vedi anche: 2026-10-04_20_Malesia_Selangor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -778,7 +762,6 @@
           <t>Airfilter Engineering (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -801,7 +784,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (Matrade, MMU Career Connect): produttore ISO9001 dal 1993 di essiccatori aria compressa, filtri, elementi di ricambio, separatori, scarichi automatici; sede 2, Jalan Anggerik Mokara 31/47, Section 31, Kota Kemuning, Shah Alam, Selangor. Dispone di societa' di distribuzione in Malesia, Singapore, Germania, Cina: fornitore B2B diretto. Dati telefono/email confermati da fonte indipendente oltre alla lista originale.</t>
+          <t>Verificato via ricerca web (Matrade, MMU Career Connect): produttore ISO9001 dal 1993 di essiccatori aria compressa, filtri, elementi di ricambio, separatori, scarichi automatici; sede 2, Jalan Anggerik Mokara 31/47, Section 31, Kota Kemuning, Shah Alam, Selangor. Dispone di societa' di distribuzione in Malesia, Singapore, Germania, Cina: fornitore B2B diretto. Dati telefono/email confermati da fonte indipendente oltre alla lista originale. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -836,10 +819,9 @@
           <t>+603-8023 8250</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (sito ufficiale non accessibile per fetch diretto - HTTP 403 - confermato invece tramite risultati di ricerca con indirizzo e telefono coincidenti): No. 7C, Jalan USJ 10/1J, UEP Subang Jaya, Petaling Jaya, Selangor. Produttore leader globale filtri aria, vende a OEM e rete di distributori: fornitore B2B diretto. Email non reperita.</t>
+          <t>Verificato via ricerca web (sito ufficiale non accessibile per fetch diretto - HTTP 403 - confermato invece tramite risultati di ricerca con indirizzo e telefono coincidenti): No. 7C, Jalan USJ 10/1J, UEP Subang Jaya, Petaling Jaya, Selangor. Produttore leader globale filtri aria, vende a OEM e rete di distributori: fornitore B2B diretto. Email non reperita. [DUPLICATO — vedi anche: 2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -854,7 +836,6 @@
           <t>K-FLEX Malaysia Sdn Bhd (K-Flex (M) Sdn Bhd)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -865,8 +846,6 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Verificato via ricerca web (Hiredly, Jobstore, Jobstreet): parte del gruppo italiano L'Isolante K-Flex, produce e distribuisce isolamento elastomerico termico/acustico per HVAC, condotte e processi industriali; sede Blok C Lot 2752, Jalan Raja Nong, Taman Sentosa, Klang, Selangor. NOTA: categoria prodotto (isolamento per condotte) e' adiacente al perimetro ventilazione/filtrazione definito (filtri/ventilatori/condotte/valvole/cicloni/maniche) ma non coincide esattamente: verificare rilevanza con il cliente. Telefono/email non reperiti.</t>
@@ -874,7 +853,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -884,7 +863,6 @@
           <t>Singuan Blasting Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Selangor</t>
@@ -895,11 +873,9 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (MachineTools.com): produttore/fornitore di macchine per sabbiatura standard e custom, dust collector industriali, macchine per deflashing plastica e materiali abrasivi; sede 39, Jalan Utarid U5/22, Mah Sing Industrial Area, Shah Alam, Selangor. Core business e' attrezzature per sabbiatura con dust collector come linea di prodotto: fornitore B2B diretto, non azienda che esercita essa stessa lavorazioni/officina. Telefono/email non reperiti.</t>
+          <t>Verificato via ricerca web (MachineTools.com): produttore/fornitore di macchine per sabbiatura standard e custom, dust collector industriali, macchine per deflashing plastica e materiali abrasivi; sede 39, Jalan Utarid U5/22, Mah Sing Industrial Area, Shah Alam, Selangor. Core business e' attrezzature per sabbiatura con dust collector come linea di prodotto: fornitore B2B diretto, non azienda che esercita essa stessa lavorazioni/officina. Telefono/email non reperiti. [DUPLICATO — vedi anche: 2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
